--- a/output/Hubei/黄冈市_news.xlsx
+++ b/output/Hubei/黄冈市_news.xlsx
@@ -565,14 +565,12 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/014D644DA2764326A8ED3F3920930E1A</t>
@@ -639,14 +637,12 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/92BA35CDA1654CD88E1B4A4E7BCC9AD3</t>
@@ -713,14 +709,12 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/AF671E470FC6432FB0B3641F2DCE7187</t>
@@ -787,14 +781,12 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/9d94b3b61ab84dbda850bb437e290244</t>
@@ -861,14 +853,12 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/a5839dfe2b1f48fdbab13dc119849862</t>
@@ -935,14 +925,12 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>483</v>
+        <v>512</v>
       </c>
       <c r="M7" t="n">
         <v>7</v>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/c80423205f09473987b785a19bdcd8b9</t>
@@ -1009,14 +997,12 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>331</v>
+        <v>361</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/73263372533a4aa5a95129f3263742f5</t>
@@ -1083,14 +1069,12 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>442</v>
+        <v>472</v>
       </c>
       <c r="M9" t="n">
         <v>35</v>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/614b3aad244843bd95d27f522b49e464</t>
@@ -1157,14 +1141,12 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>364</v>
+        <v>394</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/3e08ceb1c9ec4fdcb5931d5a96d21df3</t>
@@ -1231,14 +1213,12 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>449</v>
+        <v>482</v>
       </c>
       <c r="M11" t="n">
         <v>43</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/c97872ef1f3b418c9fffbfdad4d22152</t>
@@ -1305,14 +1285,12 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>412</v>
+        <v>442</v>
       </c>
       <c r="M12" t="n">
         <v>27</v>
       </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/ff8cb8e39e1a49f39f7142fca87a26cd</t>
@@ -1379,14 +1357,12 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>398</v>
+        <v>427</v>
       </c>
       <c r="M13" t="n">
         <v>21</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/fffc3e7eeae34bb09400904f3b186da1</t>
@@ -1453,14 +1429,12 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>397</v>
+        <v>420</v>
       </c>
       <c r="M14" t="n">
         <v>19</v>
       </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/407a972ae6d5474ebe13cb4c8b486dad</t>
@@ -1527,14 +1501,12 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>451</v>
+        <v>479</v>
       </c>
       <c r="M15" t="n">
         <v>6</v>
       </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/1464cb659a8748fe9be39c13e9d57cae</t>
@@ -1601,14 +1573,12 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>432</v>
+        <v>457</v>
       </c>
       <c r="M16" t="n">
         <v>27</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/eaabdf63aaa74851977cded71ad7c4f2</t>
@@ -1675,14 +1645,12 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>368</v>
+        <v>395</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/04965a7c82274bb2b17e0e4a2bb71084</t>
@@ -1749,14 +1717,12 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>446</v>
+        <v>473</v>
       </c>
       <c r="M18" t="n">
         <v>21</v>
       </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/826898e59a474be0b668c4cc4b6d2b06</t>
@@ -1823,14 +1789,12 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>502</v>
+        <v>529</v>
       </c>
       <c r="M19" t="n">
         <v>25</v>
       </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/6d1b766bde0c4ec88454ca682a80e56d</t>
@@ -1897,14 +1861,12 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>503</v>
+        <v>529</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/7f40bdbf0f9a4937b008bbdd39a0a54f</t>
@@ -1971,14 +1933,12 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>439</v>
+        <v>466</v>
       </c>
       <c r="M21" t="n">
         <v>2</v>
       </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/47e129baa9da4d00adaadfb8eb367f37</t>
@@ -2045,14 +2005,12 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>384</v>
+        <v>412</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/3844ca3190a846629fee1330aa639ff3</t>
@@ -2119,14 +2077,12 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>421</v>
+        <v>448</v>
       </c>
       <c r="M23" t="n">
         <v>3</v>
       </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/39b45742da8c47d0b587bec78d9c0293</t>
@@ -2193,14 +2149,12 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>421</v>
+        <v>446</v>
       </c>
       <c r="M24" t="n">
         <v>1</v>
       </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/83976dc6684b4a1bab5eb7920e248d8b</t>
@@ -2267,14 +2221,12 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>424</v>
+        <v>451</v>
       </c>
       <c r="M25" t="n">
         <v>3</v>
       </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/e0e5bf9855ea403d9458a59512aee465</t>
@@ -2341,14 +2293,12 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>386</v>
+        <v>413</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/e5c332942942413c87ad715b8f0f8368</t>
@@ -2415,14 +2365,12 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>398</v>
+        <v>426</v>
       </c>
       <c r="M27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/1047ffc93840484b9e8bbc486bf98cbc</t>
@@ -2489,14 +2437,12 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>331</v>
+        <v>358</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/60184b80285c47a79e7612bd4574c879</t>
@@ -2563,14 +2509,12 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>539</v>
+        <v>565</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/39532b301cf44cf589c4caa2ac45fd9c</t>
@@ -2637,14 +2581,12 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>324</v>
+        <v>353</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/f0e9a070376d4e51bab67e1878883ced</t>
@@ -2711,14 +2653,12 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>331</v>
+        <v>358</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/d23632b2057b44609a1c1b38a43262f5</t>
@@ -2785,14 +2725,12 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>345</v>
+        <v>370</v>
       </c>
       <c r="M32" t="n">
         <v>1</v>
       </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/50bb433f13654cb68da270b89ad31d05</t>
@@ -2859,14 +2797,12 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>553</v>
+        <v>579</v>
       </c>
       <c r="M33" t="n">
         <v>1</v>
       </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/22002847cea34151a5948fc43dc1d531</t>
@@ -2933,14 +2869,12 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>333</v>
+        <v>361</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/19f2a51eb72d4d6d9dc375a283c3c2ee</t>
@@ -3007,14 +2941,12 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>327</v>
+        <v>358</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/9cfac92ea3e24036bdffd348b5822b65</t>
@@ -3081,14 +3013,12 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>323</v>
+        <v>352</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/a2ce20b75fbc4eb48238baaecd9c5394</t>
@@ -3155,14 +3085,12 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>336</v>
+        <v>364</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/8faaa06a5537449b973b5015fb445cb4</t>
@@ -3229,14 +3157,12 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>333</v>
+        <v>361</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/38d3d77b9995496a95ba7a273d969670</t>
@@ -3303,14 +3229,12 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>333</v>
+        <v>361</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/63739a61c1284892bf5f2ae270d1952b</t>
@@ -3377,14 +3301,12 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>329</v>
+        <v>359</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/cf78744ec44f470c87001e48f8b1d446</t>
@@ -3451,14 +3373,12 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>326</v>
+        <v>354</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/5f52209685da4940ad55bfa27bb514fc</t>
@@ -3525,14 +3445,12 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>333</v>
+        <v>361</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/8b750af94fde47cdad38e18be5e96f04</t>
@@ -3599,14 +3517,12 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>331</v>
+        <v>357</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/7454829a590b4412856177c6855d454b</t>
@@ -3673,14 +3589,12 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>332</v>
+        <v>360</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/875d61fc4c6a4a9ebbab2252cc54ab5a</t>
@@ -3747,14 +3661,12 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>336</v>
+        <v>363</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/fdfa84d1740f4276b2ee1dafdb716b4e</t>
@@ -3821,14 +3733,12 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>336</v>
+        <v>363</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/600349cf0acb4322bf9cc7231bc733bd</t>
@@ -3895,14 +3805,12 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>329</v>
+        <v>357</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/f85108760d0d457a92b407a77c11d86b</t>
@@ -3969,14 +3877,12 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>324</v>
+        <v>351</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/421f0c09491b459090df5213868f212b</t>
@@ -4043,14 +3949,12 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>327</v>
+        <v>354</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
       </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/e708bd79808d480a842f725615939af3</t>
@@ -4117,14 +4021,12 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>363</v>
+        <v>394</v>
       </c>
       <c r="M50" t="n">
         <v>2</v>
       </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/8835e06b711846de96fb62aa722a9ee7</t>
@@ -4191,14 +4093,12 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>441</v>
+        <v>467</v>
       </c>
       <c r="M51" t="n">
         <v>1</v>
       </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/027ed383abfe45f481ebfb19799b5dfc</t>
@@ -4265,14 +4165,12 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>462</v>
+        <v>488</v>
       </c>
       <c r="M52" t="n">
         <v>9</v>
       </c>
-      <c r="N52" t="n">
-        <v>0</v>
-      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/89c536558d29428291ae89f2f3072b06</t>
@@ -4339,14 +4237,12 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>365</v>
+        <v>391</v>
       </c>
       <c r="M53" t="n">
         <v>2</v>
       </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/f9fbef0057904ba6ada568d03030d1e2</t>
@@ -4413,14 +4309,12 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>400</v>
+        <v>427</v>
       </c>
       <c r="M54" t="n">
         <v>3</v>
       </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/d1d9fa62959e4c17a2879e9b428ca7d8</t>
@@ -4487,14 +4381,12 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>459</v>
+        <v>486</v>
       </c>
       <c r="M55" t="n">
         <v>1</v>
       </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/d9501421c87c4153a4b853f74aab1fd4</t>
@@ -4561,14 +4453,12 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>330</v>
+        <v>356</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
       </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/f6855afb4cc64c8192f920b8604343c9</t>
@@ -4635,14 +4525,12 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>433</v>
+        <v>459</v>
       </c>
       <c r="M57" t="n">
         <v>4</v>
       </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/d76fa693a8d64681a8987bb030f8faf5</t>
@@ -4709,14 +4597,12 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>395</v>
+        <v>421</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
       </c>
-      <c r="N58" t="n">
-        <v>0</v>
-      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/94e559a2030643cc812f09e8ba49d3ba</t>
@@ -4783,14 +4669,12 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>404</v>
+        <v>429</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
       </c>
-      <c r="N59" t="n">
-        <v>0</v>
-      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/573bf6896965415e891654eac4efa11b</t>
@@ -4857,14 +4741,12 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>376</v>
+        <v>402</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
       </c>
-      <c r="N60" t="n">
-        <v>0</v>
-      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/36d9a609a7464bc5a87f7a1f3e998eb4</t>
@@ -4931,14 +4813,12 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>471</v>
+        <v>497</v>
       </c>
       <c r="M61" t="n">
         <v>16</v>
       </c>
-      <c r="N61" t="n">
-        <v>0</v>
-      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/8c320af5ccb2479395c9e456ddfd0690</t>
@@ -5005,14 +4885,12 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>506</v>
+        <v>532</v>
       </c>
       <c r="M62" t="n">
         <v>20</v>
       </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/29289d221ff942d3aa13530a7f7d068e</t>
@@ -5079,14 +4957,12 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>412</v>
+        <v>439</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
       </c>
-      <c r="N63" t="n">
-        <v>0</v>
-      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/23f40bf080c442fc93566d37bcc88e2e</t>
@@ -5153,14 +5029,12 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>439</v>
+        <v>464</v>
       </c>
       <c r="M64" t="n">
         <v>13</v>
       </c>
-      <c r="N64" t="n">
-        <v>0</v>
-      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/398778a6567e45a7a583ac0ea7868881</t>
@@ -5227,14 +5101,12 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>315</v>
+        <v>341</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
       </c>
-      <c r="N65" t="n">
-        <v>0</v>
-      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/07aebbdf718049eaba9599bdb602672b</t>
@@ -5301,14 +5173,12 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>445</v>
+        <v>473</v>
       </c>
       <c r="M66" t="n">
         <v>12</v>
       </c>
-      <c r="N66" t="n">
-        <v>0</v>
-      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/7ccd09d0ea104f33acd45b6e4e491b18</t>
@@ -5375,14 +5245,12 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>449</v>
+        <v>475</v>
       </c>
       <c r="M67" t="n">
-        <v>23</v>
-      </c>
-      <c r="N67" t="n">
-        <v>0</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/5ea1c611fd93471fa0ae3181187e5284</t>
@@ -5449,14 +5317,12 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>473</v>
+        <v>500</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
       </c>
-      <c r="N68" t="n">
-        <v>0</v>
-      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/b1282623b2cd44689e58a80f099718eb</t>
@@ -5523,14 +5389,12 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>333</v>
+        <v>361</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
       </c>
-      <c r="N69" t="n">
-        <v>0</v>
-      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/b6a70943d17e4574a54a1db3b18adc7d</t>
@@ -5597,14 +5461,12 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>326</v>
+        <v>353</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
       </c>
-      <c r="N70" t="n">
-        <v>0</v>
-      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/d6ab75b81e1548b3ba40a0c1fb6895f0</t>
@@ -5671,14 +5533,12 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>400</v>
+        <v>427</v>
       </c>
       <c r="M71" t="n">
         <v>10</v>
       </c>
-      <c r="N71" t="n">
-        <v>0</v>
-      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/7ab4eb172f7343f4973eb8f5d90478a5</t>
@@ -5745,14 +5605,12 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>427</v>
+        <v>453</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
       </c>
-      <c r="N72" t="n">
-        <v>0</v>
-      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/ef20a289d7b041848f9cc984840270e1</t>
@@ -5819,14 +5677,12 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>472</v>
+        <v>499</v>
       </c>
       <c r="M73" t="n">
         <v>1</v>
       </c>
-      <c r="N73" t="n">
-        <v>0</v>
-      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/27f683a65c444b2186820667dc16c500</t>
@@ -5893,14 +5749,12 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>422</v>
+        <v>449</v>
       </c>
       <c r="M74" t="n">
         <v>2</v>
       </c>
-      <c r="N74" t="n">
-        <v>0</v>
-      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/e966589fceaf4702bfe8609b5de2cfe8</t>
@@ -5967,14 +5821,12 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>325</v>
+        <v>355</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
       </c>
-      <c r="N75" t="n">
-        <v>0</v>
-      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/96d65a85a1c24246b42c4418a11bd381</t>
@@ -6041,14 +5893,12 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>327</v>
+        <v>354</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
       </c>
-      <c r="N76" t="n">
-        <v>0</v>
-      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/03e61abfdb854ca48c051c4fca6783ab</t>
@@ -6115,14 +5965,12 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>382</v>
+        <v>409</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
       </c>
-      <c r="N77" t="n">
-        <v>0</v>
-      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/f5fe18b385ba4dea8c38eaefa9a17b3a</t>
@@ -6189,14 +6037,12 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>331</v>
+        <v>358</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
       </c>
-      <c r="N78" t="n">
-        <v>0</v>
-      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/1531f41dee2049afb46238d8d79fb693</t>
@@ -6263,14 +6109,12 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>405</v>
+        <v>432</v>
       </c>
       <c r="M79" t="n">
         <v>9</v>
       </c>
-      <c r="N79" t="n">
-        <v>0</v>
-      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/dc95d29d75df4b8a9ed6ef533ab0bdcc</t>
@@ -6337,14 +6181,12 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>327</v>
+        <v>355</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
       </c>
-      <c r="N80" t="n">
-        <v>0</v>
-      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/408295d58f3e482db2d90a363ddc62c4</t>
@@ -6411,14 +6253,12 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>328</v>
+        <v>355</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
       </c>
-      <c r="N81" t="n">
-        <v>0</v>
-      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/95388b977f8f47478248df231fc7b6a2</t>
@@ -6485,14 +6325,12 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>334</v>
+        <v>359</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
       </c>
-      <c r="N82" t="n">
-        <v>0</v>
-      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/2acd4bdaa40a4f118fb60ad7a9c1d021</t>
@@ -6559,14 +6397,12 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>338</v>
+        <v>366</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
       </c>
-      <c r="N83" t="n">
-        <v>0</v>
-      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/da148fea56a843da9a299aae8f1071ff</t>
@@ -6633,14 +6469,12 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
       </c>
-      <c r="N84" t="n">
-        <v>0</v>
-      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/34150f849f5a4f7bbd2290fa8ab5ab5d</t>
@@ -6707,14 +6541,12 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>329</v>
+        <v>357</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
       </c>
-      <c r="N85" t="n">
-        <v>0</v>
-      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/5b50bec09be94a958d0d94ec8b9187ba</t>
@@ -6781,14 +6613,12 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>324</v>
+        <v>351</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
       </c>
-      <c r="N86" t="n">
-        <v>0</v>
-      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/ea29aa6915c64d02b0d6961a1443b6b5</t>
@@ -6855,14 +6685,12 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>328</v>
+        <v>355</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
       </c>
-      <c r="N87" t="n">
-        <v>0</v>
-      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/3c1e0b28beba4f8e8535bd8fea9de335</t>
@@ -6929,14 +6757,12 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
       </c>
-      <c r="N88" t="n">
-        <v>0</v>
-      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/3a83799d8bc64129976e140ba5ae5885</t>
@@ -7003,14 +6829,12 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>318</v>
+        <v>343</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
       </c>
-      <c r="N89" t="n">
-        <v>0</v>
-      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/314d89b0c6c848ccb5bda062e8a1c094</t>
@@ -7077,14 +6901,12 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>324</v>
+        <v>350</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
       </c>
-      <c r="N90" t="n">
-        <v>0</v>
-      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/2a4b993753714502afa50ec1d5339f5a</t>
@@ -7151,14 +6973,12 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>332</v>
+        <v>358</v>
       </c>
       <c r="M91" t="n">
         <v>0</v>
       </c>
-      <c r="N91" t="n">
-        <v>0</v>
-      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/2aea3d2e0c7e4f679eb5b59f6f4a3192</t>
@@ -7225,14 +7045,12 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>328</v>
+        <v>355</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
       </c>
-      <c r="N92" t="n">
-        <v>0</v>
-      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/f6e8c9dcbf524b65a4bac59755d7c651</t>
@@ -7299,14 +7117,12 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
       </c>
-      <c r="N93" t="n">
-        <v>0</v>
-      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/93d040c153db4ff48a593f85cf465044</t>
@@ -7373,14 +7189,12 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="M94" t="n">
         <v>0</v>
       </c>
-      <c r="N94" t="n">
-        <v>0</v>
-      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/8223f072e31d4c40adc598c728e31933</t>
@@ -7447,14 +7261,12 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="M95" t="n">
         <v>0</v>
       </c>
-      <c r="N95" t="n">
-        <v>0</v>
-      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/572c27cc316841898871811c0be7295b</t>
@@ -7521,14 +7333,12 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="M96" t="n">
         <v>26</v>
       </c>
-      <c r="N96" t="n">
-        <v>0</v>
-      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/69e726b58b13478bb633905c84036488</t>
@@ -7595,14 +7405,12 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>486</v>
+        <v>513</v>
       </c>
       <c r="M97" t="n">
         <v>19</v>
       </c>
-      <c r="N97" t="n">
-        <v>0</v>
-      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/5d64b9834d604648853c906cda386d42</t>
@@ -7669,14 +7477,12 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>574</v>
+        <v>602</v>
       </c>
       <c r="M98" t="n">
         <v>23</v>
       </c>
-      <c r="N98" t="n">
-        <v>0</v>
-      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/6064635eb9b14fabac88f296de6a6a7b</t>
@@ -7743,14 +7549,12 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>545</v>
+        <v>572</v>
       </c>
       <c r="M99" t="n">
         <v>28</v>
       </c>
-      <c r="N99" t="n">
-        <v>0</v>
-      </c>
+      <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/4430293242a54591823d5b5797867644</t>
@@ -7817,14 +7621,12 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>391</v>
+        <v>417</v>
       </c>
       <c r="M100" t="n">
         <v>0</v>
       </c>
-      <c r="N100" t="n">
-        <v>0</v>
-      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/bea105532c1f45f6b1d6ac5b990c2f90</t>
@@ -7891,14 +7693,12 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>451</v>
+        <v>478</v>
       </c>
       <c r="M101" t="n">
         <v>0</v>
       </c>
-      <c r="N101" t="n">
-        <v>0</v>
-      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/c7678f532b3b4a66841a47f5d3e1b067</t>
@@ -7965,14 +7765,12 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>400</v>
+        <v>429</v>
       </c>
       <c r="M102" t="n">
         <v>0</v>
       </c>
-      <c r="N102" t="n">
-        <v>0</v>
-      </c>
+      <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/ed1b949b8d9b407dbfe6a43446185b14</t>
@@ -8039,14 +7837,12 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="M103" t="n">
         <v>35</v>
       </c>
-      <c r="N103" t="n">
-        <v>0</v>
-      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/7f8b60ab3f7349f78fe735e1533b5919</t>
@@ -8113,14 +7909,12 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M104" t="n">
         <v>17</v>
       </c>
-      <c r="N104" t="n">
-        <v>0</v>
-      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/24e24fe1818843aa94b091aa10fcad56</t>
@@ -8187,14 +7981,12 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>393</v>
+        <v>418</v>
       </c>
       <c r="M105" t="n">
         <v>16</v>
       </c>
-      <c r="N105" t="n">
-        <v>0</v>
-      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/eba20aab7f4345128611b450ff1fbef2</t>
@@ -8261,14 +8053,12 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>388</v>
+        <v>415</v>
       </c>
       <c r="M106" t="n">
         <v>9</v>
       </c>
-      <c r="N106" t="n">
-        <v>0</v>
-      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/e0f70e1418914bec864d9abddca6a372</t>
@@ -8335,14 +8125,12 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>408</v>
+        <v>435</v>
       </c>
       <c r="M107" t="n">
         <v>1</v>
       </c>
-      <c r="N107" t="n">
-        <v>0</v>
-      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/8a1ed09628874bb58b3de354ab3bd0f0</t>
@@ -8409,14 +8197,12 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>373</v>
+        <v>400</v>
       </c>
       <c r="M108" t="n">
         <v>1</v>
       </c>
-      <c r="N108" t="n">
-        <v>0</v>
-      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/377fc7590e4a4311b85e52312a6136b9</t>
@@ -8483,14 +8269,12 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>376</v>
+        <v>403</v>
       </c>
       <c r="M109" t="n">
         <v>0</v>
       </c>
-      <c r="N109" t="n">
-        <v>0</v>
-      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr">
         <is>
           <t>http://data.hg.gov.cn:3379/oportal/catalog/36658148962e4999896f1227f5e4c076</t>
